--- a/downloads/change-authority-review.xlsx
+++ b/downloads/change-authority-review.xlsx
@@ -829,7 +829,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Change Authority Review</t>
+          <t>Change Authority Review — What can the agent be allowed to change?</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/downloads/change-authority-review.xlsx
+++ b/downloads/change-authority-review.xlsx
@@ -2052,16 +2052,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$3</formula1>
     </dataValidation>
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$5:$Z$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$10:$Z$11</formula1>
     </dataValidation>
-    <dataValidation sqref="H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$13:$Z$15</formula1>
     </dataValidation>
   </dataValidations>
@@ -2265,7 +2265,7 @@
         <v/>
       </c>
       <c r="N7" s="8">
-        <f>IF(C7="","",IF(C7="Agent acts",IF(E7="","No undo path",IF(D7&lt;&gt;"Yes","Undo not tested","")),IF(C7="Preview and consent",IF(F7&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G7&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H7="","No named person gives consent",IF(I7&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J7&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K7&lt;&gt;"Changes nothing",K7&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C7="Not allowed",IF(L7&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C7="","",IF(C7="Agent acts",IF(E7="","No undo path",IF(D7&lt;&gt;"Yes","Undo not tested","")),IF(C7="Preview and consent",IF(F7&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G7&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H7="","No named person gives consent",IF(I7&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J7&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K7&lt;&gt;"Changes nothing",K7&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C7="Not allowed",IF(L7&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N8" s="8">
-        <f>IF(C8="","",IF(C8="Agent acts",IF(E8="","No undo path",IF(D8&lt;&gt;"Yes","Undo not tested","")),IF(C8="Preview and consent",IF(F8&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G8&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H8="","No named person gives consent",IF(I8&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J8&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K8&lt;&gt;"Changes nothing",K8&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C8="Not allowed",IF(L8&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C8="","",IF(C8="Agent acts",IF(E8="","No undo path",IF(D8&lt;&gt;"Yes","Undo not tested","")),IF(C8="Preview and consent",IF(F8&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G8&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H8="","No named person gives consent",IF(I8&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J8&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K8&lt;&gt;"Changes nothing",K8&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C8="Not allowed",IF(L8&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
       <c r="Z8" s="14" t="inlineStr">
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="N9" s="8">
-        <f>IF(C9="","",IF(C9="Agent acts",IF(E9="","No undo path",IF(D9&lt;&gt;"Yes","Undo not tested","")),IF(C9="Preview and consent",IF(F9&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G9&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H9="","No named person gives consent",IF(I9&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J9&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K9&lt;&gt;"Changes nothing",K9&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C9="Not allowed",IF(L9&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C9="","",IF(C9="Agent acts",IF(E9="","No undo path",IF(D9&lt;&gt;"Yes","Undo not tested","")),IF(C9="Preview and consent",IF(F9&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G9&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H9="","No named person gives consent",IF(I9&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J9&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K9&lt;&gt;"Changes nothing",K9&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C9="Not allowed",IF(L9&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
       <c r="Z9" s="14" t="inlineStr">
@@ -2374,7 +2374,7 @@
         <v/>
       </c>
       <c r="N10" s="8">
-        <f>IF(C10="","",IF(C10="Agent acts",IF(E10="","No undo path",IF(D10&lt;&gt;"Yes","Undo not tested","")),IF(C10="Preview and consent",IF(F10&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G10&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H10="","No named person gives consent",IF(I10&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J10&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K10&lt;&gt;"Changes nothing",K10&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C10="Not allowed",IF(L10&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C10="","",IF(C10="Agent acts",IF(E10="","No undo path",IF(D10&lt;&gt;"Yes","Undo not tested","")),IF(C10="Preview and consent",IF(F10&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G10&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H10="","No named person gives consent",IF(I10&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J10&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K10&lt;&gt;"Changes nothing",K10&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C10="Not allowed",IF(L10&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
       <c r="Z10" s="14" t="inlineStr">
@@ -2412,7 +2412,7 @@
         <v/>
       </c>
       <c r="N11" s="8">
-        <f>IF(C11="","",IF(C11="Agent acts",IF(E11="","No undo path",IF(D11&lt;&gt;"Yes","Undo not tested","")),IF(C11="Preview and consent",IF(F11&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G11&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H11="","No named person gives consent",IF(I11&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J11&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K11&lt;&gt;"Changes nothing",K11&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C11="Not allowed",IF(L11&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C11="","",IF(C11="Agent acts",IF(E11="","No undo path",IF(D11&lt;&gt;"Yes","Undo not tested","")),IF(C11="Preview and consent",IF(F11&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G11&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H11="","No named person gives consent",IF(I11&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J11&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K11&lt;&gt;"Changes nothing",K11&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C11="Not allowed",IF(L11&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
       <c r="Z11" s="14" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v/>
       </c>
       <c r="N12" s="8">
-        <f>IF(C12="","",IF(C12="Agent acts",IF(E12="","No undo path",IF(D12&lt;&gt;"Yes","Undo not tested","")),IF(C12="Preview and consent",IF(F12&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G12&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H12="","No named person gives consent",IF(I12&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J12&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K12&lt;&gt;"Changes nothing",K12&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C12="Not allowed",IF(L12&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C12="","",IF(C12="Agent acts",IF(E12="","No undo path",IF(D12&lt;&gt;"Yes","Undo not tested","")),IF(C12="Preview and consent",IF(F12&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G12&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H12="","No named person gives consent",IF(I12&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J12&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K12&lt;&gt;"Changes nothing",K12&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C12="Not allowed",IF(L12&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         <v/>
       </c>
       <c r="N13" s="8">
-        <f>IF(C13="","",IF(C13="Agent acts",IF(E13="","No undo path",IF(D13&lt;&gt;"Yes","Undo not tested","")),IF(C13="Preview and consent",IF(F13&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G13&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H13="","No named person gives consent",IF(I13&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J13&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K13&lt;&gt;"Changes nothing",K13&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C13="Not allowed",IF(L13&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C13="","",IF(C13="Agent acts",IF(E13="","No undo path",IF(D13&lt;&gt;"Yes","Undo not tested","")),IF(C13="Preview and consent",IF(F13&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G13&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H13="","No named person gives consent",IF(I13&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J13&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K13&lt;&gt;"Changes nothing",K13&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C13="Not allowed",IF(L13&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         <v/>
       </c>
       <c r="N14" s="8">
-        <f>IF(C14="","",IF(C14="Agent acts",IF(E14="","No undo path",IF(D14&lt;&gt;"Yes","Undo not tested","")),IF(C14="Preview and consent",IF(F14&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G14&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H14="","No named person gives consent",IF(I14&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J14&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K14&lt;&gt;"Changes nothing",K14&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C14="Not allowed",IF(L14&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C14="","",IF(C14="Agent acts",IF(E14="","No undo path",IF(D14&lt;&gt;"Yes","Undo not tested","")),IF(C14="Preview and consent",IF(F14&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G14&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H14="","No named person gives consent",IF(I14&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J14&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K14&lt;&gt;"Changes nothing",K14&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C14="Not allowed",IF(L14&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
         <v/>
       </c>
       <c r="N15" s="8">
-        <f>IF(C15="","",IF(C15="Agent acts",IF(E15="","No undo path",IF(D15&lt;&gt;"Yes","Undo not tested","")),IF(C15="Preview and consent",IF(F15&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G15&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H15="","No named person gives consent",IF(I15&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J15&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K15&lt;&gt;"Changes nothing",K15&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C15="Not allowed",IF(L15&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C15="","",IF(C15="Agent acts",IF(E15="","No undo path",IF(D15&lt;&gt;"Yes","Undo not tested","")),IF(C15="Preview and consent",IF(F15&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G15&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H15="","No named person gives consent",IF(I15&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J15&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K15&lt;&gt;"Changes nothing",K15&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C15="Not allowed",IF(L15&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v/>
       </c>
       <c r="N16" s="8">
-        <f>IF(C16="","",IF(C16="Agent acts",IF(E16="","No undo path",IF(D16&lt;&gt;"Yes","Undo not tested","")),IF(C16="Preview and consent",IF(F16&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G16&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H16="","No named person gives consent",IF(I16&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J16&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K16&lt;&gt;"Changes nothing",K16&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C16="Not allowed",IF(L16&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C16="","",IF(C16="Agent acts",IF(E16="","No undo path",IF(D16&lt;&gt;"Yes","Undo not tested","")),IF(C16="Preview and consent",IF(F16&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G16&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H16="","No named person gives consent",IF(I16&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J16&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K16&lt;&gt;"Changes nothing",K16&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C16="Not allowed",IF(L16&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
         <v/>
       </c>
       <c r="N17" s="8">
-        <f>IF(C17="","",IF(C17="Agent acts",IF(E17="","No undo path",IF(D17&lt;&gt;"Yes","Undo not tested","")),IF(C17="Preview and consent",IF(F17&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G17&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H17="","No named person gives consent",IF(I17&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J17&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K17&lt;&gt;"Changes nothing",K17&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C17="Not allowed",IF(L17&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C17="","",IF(C17="Agent acts",IF(E17="","No undo path",IF(D17&lt;&gt;"Yes","Undo not tested","")),IF(C17="Preview and consent",IF(F17&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G17&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H17="","No named person gives consent",IF(I17&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J17&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K17&lt;&gt;"Changes nothing",K17&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C17="Not allowed",IF(L17&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         <v/>
       </c>
       <c r="N18" s="8">
-        <f>IF(C18="","",IF(C18="Agent acts",IF(E18="","No undo path",IF(D18&lt;&gt;"Yes","Undo not tested","")),IF(C18="Preview and consent",IF(F18&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G18&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H18="","No named person gives consent",IF(I18&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J18&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K18&lt;&gt;"Changes nothing",K18&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C18="Not allowed",IF(L18&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C18="","",IF(C18="Agent acts",IF(E18="","No undo path",IF(D18&lt;&gt;"Yes","Undo not tested","")),IF(C18="Preview and consent",IF(F18&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G18&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H18="","No named person gives consent",IF(I18&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J18&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K18&lt;&gt;"Changes nothing",K18&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C18="Not allowed",IF(L18&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
         <v/>
       </c>
       <c r="N19" s="8">
-        <f>IF(C19="","",IF(C19="Agent acts",IF(E19="","No undo path",IF(D19&lt;&gt;"Yes","Undo not tested","")),IF(C19="Preview and consent",IF(F19&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G19&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H19="","No named person gives consent",IF(I19&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J19&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K19&lt;&gt;"Changes nothing",K19&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C19="Not allowed",IF(L19&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C19="","",IF(C19="Agent acts",IF(E19="","No undo path",IF(D19&lt;&gt;"Yes","Undo not tested","")),IF(C19="Preview and consent",IF(F19&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G19&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H19="","No named person gives consent",IF(I19&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J19&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K19&lt;&gt;"Changes nothing",K19&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C19="Not allowed",IF(L19&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v/>
       </c>
       <c r="N20" s="8">
-        <f>IF(C20="","",IF(C20="Agent acts",IF(E20="","No undo path",IF(D20&lt;&gt;"Yes","Undo not tested","")),IF(C20="Preview and consent",IF(F20&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G20&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H20="","No named person gives consent",IF(I20&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J20&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K20&lt;&gt;"Changes nothing",K20&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C20="Not allowed",IF(L20&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C20="","",IF(C20="Agent acts",IF(E20="","No undo path",IF(D20&lt;&gt;"Yes","Undo not tested","")),IF(C20="Preview and consent",IF(F20&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G20&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H20="","No named person gives consent",IF(I20&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J20&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K20&lt;&gt;"Changes nothing",K20&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C20="Not allowed",IF(L20&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         <v/>
       </c>
       <c r="N21" s="8">
-        <f>IF(C21="","",IF(C21="Agent acts",IF(E21="","No undo path",IF(D21&lt;&gt;"Yes","Undo not tested","")),IF(C21="Preview and consent",IF(F21&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G21&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H21="","No named person gives consent",IF(I21&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J21&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K21&lt;&gt;"Changes nothing",K21&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C21="Not allowed",IF(L21&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C21="","",IF(C21="Agent acts",IF(E21="","No undo path",IF(D21&lt;&gt;"Yes","Undo not tested","")),IF(C21="Preview and consent",IF(F21&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G21&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H21="","No named person gives consent",IF(I21&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J21&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K21&lt;&gt;"Changes nothing",K21&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C21="Not allowed",IF(L21&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
         <v/>
       </c>
       <c r="N22" s="8">
-        <f>IF(C22="","",IF(C22="Agent acts",IF(E22="","No undo path",IF(D22&lt;&gt;"Yes","Undo not tested","")),IF(C22="Preview and consent",IF(F22&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G22&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H22="","No named person gives consent",IF(I22&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J22&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K22&lt;&gt;"Changes nothing",K22&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C22="Not allowed",IF(L22&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C22="","",IF(C22="Agent acts",IF(E22="","No undo path",IF(D22&lt;&gt;"Yes","Undo not tested","")),IF(C22="Preview and consent",IF(F22&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G22&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H22="","No named person gives consent",IF(I22&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J22&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K22&lt;&gt;"Changes nothing",K22&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C22="Not allowed",IF(L22&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="N23" s="8">
-        <f>IF(C23="","",IF(C23="Agent acts",IF(E23="","No undo path",IF(D23&lt;&gt;"Yes","Undo not tested","")),IF(C23="Preview and consent",IF(F23&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G23&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H23="","No named person gives consent",IF(I23&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J23&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K23&lt;&gt;"Changes nothing",K23&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C23="Not allowed",IF(L23&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C23="","",IF(C23="Agent acts",IF(E23="","No undo path",IF(D23&lt;&gt;"Yes","Undo not tested","")),IF(C23="Preview and consent",IF(F23&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G23&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H23="","No named person gives consent",IF(I23&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J23&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K23&lt;&gt;"Changes nothing",K23&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C23="Not allowed",IF(L23&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
         <v/>
       </c>
       <c r="N24" s="8">
-        <f>IF(C24="","",IF(C24="Agent acts",IF(E24="","No undo path",IF(D24&lt;&gt;"Yes","Undo not tested","")),IF(C24="Preview and consent",IF(F24&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G24&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H24="","No named person gives consent",IF(I24&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J24&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K24&lt;&gt;"Changes nothing",K24&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C24="Not allowed",IF(L24&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C24="","",IF(C24="Agent acts",IF(E24="","No undo path",IF(D24&lt;&gt;"Yes","Undo not tested","")),IF(C24="Preview and consent",IF(F24&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G24&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H24="","No named person gives consent",IF(I24&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J24&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K24&lt;&gt;"Changes nothing",K24&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C24="Not allowed",IF(L24&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         <v/>
       </c>
       <c r="N25" s="8">
-        <f>IF(C25="","",IF(C25="Agent acts",IF(E25="","No undo path",IF(D25&lt;&gt;"Yes","Undo not tested","")),IF(C25="Preview and consent",IF(F25&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G25&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H25="","No named person gives consent",IF(I25&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J25&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K25&lt;&gt;"Changes nothing",K25&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C25="Not allowed",IF(L25&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C25="","",IF(C25="Agent acts",IF(E25="","No undo path",IF(D25&lt;&gt;"Yes","Undo not tested","")),IF(C25="Preview and consent",IF(F25&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G25&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H25="","No named person gives consent",IF(I25&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J25&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K25&lt;&gt;"Changes nothing",K25&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C25="Not allowed",IF(L25&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="N26" s="8">
-        <f>IF(C26="","",IF(C26="Agent acts",IF(E26="","No undo path",IF(D26&lt;&gt;"Yes","Undo not tested","")),IF(C26="Preview and consent",IF(F26&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G26&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H26="","No named person gives consent",IF(I26&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J26&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K26&lt;&gt;"Changes nothing",K26&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C26="Not allowed",IF(L26&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C26="","",IF(C26="Agent acts",IF(E26="","No undo path",IF(D26&lt;&gt;"Yes","Undo not tested","")),IF(C26="Preview and consent",IF(F26&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G26&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H26="","No named person gives consent",IF(I26&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J26&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K26&lt;&gt;"Changes nothing",K26&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C26="Not allowed",IF(L26&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -3122,19 +3122,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$2</formula1>
     </dataValidation>
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$4:$Z$6</formula1>
     </dataValidation>
-    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$8:$Z$11</formula1>
     </dataValidation>
-    <dataValidation sqref="E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this authority" error="This column is for Agent acts actions. Change the authority on the Action Inventory first." type="custom">
+    <dataValidation sqref="E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this authority" error="This column is for Agent acts actions. Change the authority on the Action Inventory first." type="custom">
       <formula1>$C7="Agent acts"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this authority" error="This column is for Preview and consent actions. Change the authority on the Action Inventory first." type="custom">
+    <dataValidation sqref="H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this authority" error="This column is for Preview and consent actions. Change the authority on the Action Inventory first." type="custom">
       <formula1>$C7="Preview and consent"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3635,7 +3635,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="N50" s="8">
-        <f>IF(C50="","",IF(C50="Agent acts",IF(E50="","No undo path",IF(D50&lt;&gt;"Yes","Undo not tested","")),IF(C50="Preview and consent",IF(F50&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G50&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H50="","No named person gives consent",IF(I50&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J50&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K50&lt;&gt;"Changes nothing",K50&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C50="Not allowed",IF(L50&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C50="","",IF(C50="Agent acts",IF(E50="","No undo path",IF(D50&lt;&gt;"Yes","Undo not tested","")),IF(C50="Preview and consent",IF(F50&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G50&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H50="","No named person gives consent",IF(I50&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J50&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K50&lt;&gt;"Changes nothing",K50&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C50="Not allowed",IF(L50&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
         <v/>
       </c>
       <c r="N51" s="8">
-        <f>IF(C51="","",IF(C51="Agent acts",IF(E51="","No undo path",IF(D51&lt;&gt;"Yes","Undo not tested","")),IF(C51="Preview and consent",IF(F51&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G51&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H51="","No named person gives consent",IF(I51&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J51&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K51&lt;&gt;"Changes nothing",K51&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C51="Not allowed",IF(L51&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C51="","",IF(C51="Agent acts",IF(E51="","No undo path",IF(D51&lt;&gt;"Yes","Undo not tested","")),IF(C51="Preview and consent",IF(F51&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G51&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H51="","No named person gives consent",IF(I51&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J51&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K51&lt;&gt;"Changes nothing",K51&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C51="Not allowed",IF(L51&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
         <v/>
       </c>
       <c r="N52" s="8">
-        <f>IF(C52="","",IF(C52="Agent acts",IF(E52="","No undo path",IF(D52&lt;&gt;"Yes","Undo not tested","")),IF(C52="Preview and consent",IF(F52&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G52&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H52="","No named person gives consent",IF(I52&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J52&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K52&lt;&gt;"Changes nothing",K52&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C52="Not allowed",IF(L52&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C52="","",IF(C52="Agent acts",IF(E52="","No undo path",IF(D52&lt;&gt;"Yes","Undo not tested","")),IF(C52="Preview and consent",IF(F52&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G52&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H52="","No named person gives consent",IF(I52&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J52&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K52&lt;&gt;"Changes nothing",K52&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C52="Not allowed",IF(L52&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v/>
       </c>
       <c r="N53" s="8">
-        <f>IF(C53="","",IF(C53="Agent acts",IF(E53="","No undo path",IF(D53&lt;&gt;"Yes","Undo not tested","")),IF(C53="Preview and consent",IF(F53&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G53&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H53="","No named person gives consent",IF(I53&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J53&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K53&lt;&gt;"Changes nothing",K53&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C53="Not allowed",IF(L53&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C53="","",IF(C53="Agent acts",IF(E53="","No undo path",IF(D53&lt;&gt;"Yes","Undo not tested","")),IF(C53="Preview and consent",IF(F53&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G53&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H53="","No named person gives consent",IF(I53&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J53&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K53&lt;&gt;"Changes nothing",K53&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C53="Not allowed",IF(L53&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v/>
       </c>
       <c r="N54" s="8">
-        <f>IF(C54="","",IF(C54="Agent acts",IF(E54="","No undo path",IF(D54&lt;&gt;"Yes","Undo not tested","")),IF(C54="Preview and consent",IF(F54&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G54&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H54="","No named person gives consent",IF(I54&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J54&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K54&lt;&gt;"Changes nothing",K54&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C54="Not allowed",IF(L54&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C54="","",IF(C54="Agent acts",IF(E54="","No undo path",IF(D54&lt;&gt;"Yes","Undo not tested","")),IF(C54="Preview and consent",IF(F54&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G54&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H54="","No named person gives consent",IF(I54&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J54&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K54&lt;&gt;"Changes nothing",K54&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C54="Not allowed",IF(L54&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
         <v/>
       </c>
       <c r="N55" s="8">
-        <f>IF(C55="","",IF(C55="Agent acts",IF(E55="","No undo path",IF(D55&lt;&gt;"Yes","Undo not tested","")),IF(C55="Preview and consent",IF(F55&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G55&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H55="","No named person gives consent",IF(I55&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J55&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K55&lt;&gt;"Changes nothing",K55&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C55="Not allowed",IF(L55&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C55="","",IF(C55="Agent acts",IF(E55="","No undo path",IF(D55&lt;&gt;"Yes","Undo not tested","")),IF(C55="Preview and consent",IF(F55&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G55&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H55="","No named person gives consent",IF(I55&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J55&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K55&lt;&gt;"Changes nothing",K55&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C55="Not allowed",IF(L55&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
         <v/>
       </c>
       <c r="N56" s="8">
-        <f>IF(C56="","",IF(C56="Agent acts",IF(E56="","No undo path",IF(D56&lt;&gt;"Yes","Undo not tested","")),IF(C56="Preview and consent",IF(F56&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G56&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H56="","No named person gives consent",IF(I56&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J56&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K56&lt;&gt;"Changes nothing",K56&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C56="Not allowed",IF(L56&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C56="","",IF(C56="Agent acts",IF(E56="","No undo path",IF(D56&lt;&gt;"Yes","Undo not tested","")),IF(C56="Preview and consent",IF(F56&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G56&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H56="","No named person gives consent",IF(I56&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J56&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K56&lt;&gt;"Changes nothing",K56&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C56="Not allowed",IF(L56&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
         <v/>
       </c>
       <c r="N57" s="8">
-        <f>IF(C57="","",IF(C57="Agent acts",IF(E57="","No undo path",IF(D57&lt;&gt;"Yes","Undo not tested","")),IF(C57="Preview and consent",IF(F57&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G57&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H57="","No named person gives consent",IF(I57&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J57&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K57&lt;&gt;"Changes nothing",K57&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C57="Not allowed",IF(L57&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C57="","",IF(C57="Agent acts",IF(E57="","No undo path",IF(D57&lt;&gt;"Yes","Undo not tested","")),IF(C57="Preview and consent",IF(F57&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G57&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H57="","No named person gives consent",IF(I57&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J57&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K57&lt;&gt;"Changes nothing",K57&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C57="Not allowed",IF(L57&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
         <v/>
       </c>
       <c r="N58" s="8">
-        <f>IF(C58="","",IF(C58="Agent acts",IF(E58="","No undo path",IF(D58&lt;&gt;"Yes","Undo not tested","")),IF(C58="Preview and consent",IF(F58&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G58&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H58="","No named person gives consent",IF(I58&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J58&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K58&lt;&gt;"Changes nothing",K58&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C58="Not allowed",IF(L58&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C58="","",IF(C58="Agent acts",IF(E58="","No undo path",IF(D58&lt;&gt;"Yes","Undo not tested","")),IF(C58="Preview and consent",IF(F58&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G58&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H58="","No named person gives consent",IF(I58&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J58&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K58&lt;&gt;"Changes nothing",K58&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C58="Not allowed",IF(L58&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="N59" s="8">
-        <f>IF(C59="","",IF(C59="Agent acts",IF(E59="","No undo path",IF(D59&lt;&gt;"Yes","Undo not tested","")),IF(C59="Preview and consent",IF(F59&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G59&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H59="","No named person gives consent",IF(I59&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J59&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K59&lt;&gt;"Changes nothing",K59&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C59="Not allowed",IF(L59&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C59="","",IF(C59="Agent acts",IF(E59="","No undo path",IF(D59&lt;&gt;"Yes","Undo not tested","")),IF(C59="Preview and consent",IF(F59&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G59&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H59="","No named person gives consent",IF(I59&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J59&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K59&lt;&gt;"Changes nothing",K59&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C59="Not allowed",IF(L59&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="N60" s="8">
-        <f>IF(C60="","",IF(C60="Agent acts",IF(E60="","No undo path",IF(D60&lt;&gt;"Yes","Undo not tested","")),IF(C60="Preview and consent",IF(F60&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G60&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H60="","No named person gives consent",IF(I60&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J60&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K60&lt;&gt;"Changes nothing",K60&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C60="Not allowed",IF(L60&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C60="","",IF(C60="Agent acts",IF(E60="","No undo path",IF(D60&lt;&gt;"Yes","Undo not tested","")),IF(C60="Preview and consent",IF(F60&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G60&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H60="","No named person gives consent",IF(I60&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J60&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K60&lt;&gt;"Changes nothing",K60&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C60="Not allowed",IF(L60&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
         <v/>
       </c>
       <c r="N61" s="8">
-        <f>IF(C61="","",IF(C61="Agent acts",IF(E61="","No undo path",IF(D61&lt;&gt;"Yes","Undo not tested","")),IF(C61="Preview and consent",IF(F61&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G61&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H61="","No named person gives consent",IF(I61&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J61&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K61&lt;&gt;"Changes nothing",K61&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C61="Not allowed",IF(L61&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C61="","",IF(C61="Agent acts",IF(E61="","No undo path",IF(D61&lt;&gt;"Yes","Undo not tested","")),IF(C61="Preview and consent",IF(F61&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G61&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H61="","No named person gives consent",IF(I61&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J61&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K61&lt;&gt;"Changes nothing",K61&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C61="Not allowed",IF(L61&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
         <v/>
       </c>
       <c r="N62" s="8">
-        <f>IF(C62="","",IF(C62="Agent acts",IF(E62="","No undo path",IF(D62&lt;&gt;"Yes","Undo not tested","")),IF(C62="Preview and consent",IF(F62&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G62&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H62="","No named person gives consent",IF(I62&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J62&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K62&lt;&gt;"Changes nothing",K62&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C62="Not allowed",IF(L62&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C62="","",IF(C62="Agent acts",IF(E62="","No undo path",IF(D62&lt;&gt;"Yes","Undo not tested","")),IF(C62="Preview and consent",IF(F62&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G62&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H62="","No named person gives consent",IF(I62&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J62&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K62&lt;&gt;"Changes nothing",K62&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C62="Not allowed",IF(L62&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
         <v/>
       </c>
       <c r="N63" s="8">
-        <f>IF(C63="","",IF(C63="Agent acts",IF(E63="","No undo path",IF(D63&lt;&gt;"Yes","Undo not tested","")),IF(C63="Preview and consent",IF(F63&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G63&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H63="","No named person gives consent",IF(I63&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J63&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K63&lt;&gt;"Changes nothing",K63&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C63="Not allowed",IF(L63&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C63="","",IF(C63="Agent acts",IF(E63="","No undo path",IF(D63&lt;&gt;"Yes","Undo not tested","")),IF(C63="Preview and consent",IF(F63&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G63&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H63="","No named person gives consent",IF(I63&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J63&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K63&lt;&gt;"Changes nothing",K63&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C63="Not allowed",IF(L63&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v/>
       </c>
       <c r="N64" s="8">
-        <f>IF(C64="","",IF(C64="Agent acts",IF(E64="","No undo path",IF(D64&lt;&gt;"Yes","Undo not tested","")),IF(C64="Preview and consent",IF(F64&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G64&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H64="","No named person gives consent",IF(I64&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J64&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K64&lt;&gt;"Changes nothing",K64&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C64="Not allowed",IF(L64&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C64="","",IF(C64="Agent acts",IF(E64="","No undo path",IF(D64&lt;&gt;"Yes","Undo not tested","")),IF(C64="Preview and consent",IF(F64&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G64&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H64="","No named person gives consent",IF(I64&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J64&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K64&lt;&gt;"Changes nothing",K64&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C64="Not allowed",IF(L64&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
         <v/>
       </c>
       <c r="N65" s="8">
-        <f>IF(C65="","",IF(C65="Agent acts",IF(E65="","No undo path",IF(D65&lt;&gt;"Yes","Undo not tested","")),IF(C65="Preview and consent",IF(F65&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G65&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H65="","No named person gives consent",IF(I65&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J65&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K65&lt;&gt;"Changes nothing",K65&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C65="Not allowed",IF(L65&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C65="","",IF(C65="Agent acts",IF(E65="","No undo path",IF(D65&lt;&gt;"Yes","Undo not tested","")),IF(C65="Preview and consent",IF(F65&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G65&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H65="","No named person gives consent",IF(I65&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J65&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K65&lt;&gt;"Changes nothing",K65&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C65="Not allowed",IF(L65&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
         <v/>
       </c>
       <c r="N66" s="8">
-        <f>IF(C66="","",IF(C66="Agent acts",IF(E66="","No undo path",IF(D66&lt;&gt;"Yes","Undo not tested","")),IF(C66="Preview and consent",IF(F66&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G66&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H66="","No named person gives consent",IF(I66&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J66&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K66&lt;&gt;"Changes nothing",K66&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C66="Not allowed",IF(L66&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C66="","",IF(C66="Agent acts",IF(E66="","No undo path",IF(D66&lt;&gt;"Yes","Undo not tested","")),IF(C66="Preview and consent",IF(F66&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G66&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H66="","No named person gives consent",IF(I66&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J66&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K66&lt;&gt;"Changes nothing",K66&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C66="Not allowed",IF(L66&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
         <v/>
       </c>
       <c r="N67" s="8">
-        <f>IF(C67="","",IF(C67="Agent acts",IF(E67="","No undo path",IF(D67&lt;&gt;"Yes","Undo not tested","")),IF(C67="Preview and consent",IF(F67&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G67&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H67="","No named person gives consent",IF(I67&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J67&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K67&lt;&gt;"Changes nothing",K67&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C67="Not allowed",IF(L67&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C67="","",IF(C67="Agent acts",IF(E67="","No undo path",IF(D67&lt;&gt;"Yes","Undo not tested","")),IF(C67="Preview and consent",IF(F67&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G67&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H67="","No named person gives consent",IF(I67&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J67&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K67&lt;&gt;"Changes nothing",K67&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C67="Not allowed",IF(L67&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
         <v/>
       </c>
       <c r="N68" s="8">
-        <f>IF(C68="","",IF(C68="Agent acts",IF(E68="","No undo path",IF(D68&lt;&gt;"Yes","Undo not tested","")),IF(C68="Preview and consent",IF(F68&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G68&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H68="","No named person gives consent",IF(I68&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J68&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K68&lt;&gt;"Changes nothing",K68&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C68="Not allowed",IF(L68&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C68="","",IF(C68="Agent acts",IF(E68="","No undo path",IF(D68&lt;&gt;"Yes","Undo not tested","")),IF(C68="Preview and consent",IF(F68&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G68&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H68="","No named person gives consent",IF(I68&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J68&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K68&lt;&gt;"Changes nothing",K68&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C68="Not allowed",IF(L68&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
         <v/>
       </c>
       <c r="N69" s="8">
-        <f>IF(C69="","",IF(C69="Agent acts",IF(E69="","No undo path",IF(D69&lt;&gt;"Yes","Undo not tested","")),IF(C69="Preview and consent",IF(F69&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G69&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H69="","No named person gives consent",IF(I69&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J69&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K69&lt;&gt;"Changes nothing",K69&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C69="Not allowed",IF(L69&lt;&gt;"Yes","Access not removed",""),""))))</f>
+        <f>IF(C69="","",IF(C69="Agent acts",IF(E69="","No undo path",IF(D69&lt;&gt;"Yes","Undo not tested","")),IF(C69="Preview and consent",IF(F69&lt;&gt;"Yes","Preview doesn’t show the full change",IF(G69&lt;&gt;"Yes","Preview doesn’t say what can’t be undone",IF(H69="","No named person gives consent",IF(I69&lt;&gt;"Yes","Consent is a standing default, not per change",IF(J69&lt;&gt;"Yes","Agent doesn’t act as the consenting person",IF(AND(K69&lt;&gt;"Changes nothing",K69&lt;&gt;"Revises and asks again"),"No safe outcome when consent is refused","")))))),IF(C69="Not allowed",IF(L69&lt;&gt;"Yes","Access not removed",""),"Not one of the three authority levels"))))</f>
         <v/>
       </c>
     </row>
@@ -6366,28 +6366,28 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$1:$Z$3</formula1>
     </dataValidation>
-    <dataValidation sqref="E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$5:$Z$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$10:$Z$11</formula1>
     </dataValidation>
-    <dataValidation sqref="H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$13:$Z$15</formula1>
     </dataValidation>
-    <dataValidation sqref="E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$17:$Z$19</formula1>
     </dataValidation>
-    <dataValidation sqref="K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
+    <dataValidation sqref="K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an option" error="Pick one of the options in the list." type="list">
       <formula1>$Z$21:$Z$24</formula1>
     </dataValidation>
-    <dataValidation sqref="E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this authority" error="This column is for Agent acts actions. Change the authority on the Action Inventory first." type="custom">
+    <dataValidation sqref="E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this authority" error="This column is for Agent acts actions. Change the authority on the Action Inventory first." type="custom">
       <formula1>$C50="Agent acts"</formula1>
     </dataValidation>
-    <dataValidation sqref="H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not this authority" error="This column is for Preview and consent actions. Change the authority on the Action Inventory first." type="custom">
+    <dataValidation sqref="H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not this authority" error="This column is for Preview and consent actions. Change the authority on the Action Inventory first." type="custom">
       <formula1>$C50="Preview and consent"</formula1>
     </dataValidation>
   </dataValidations>
